--- a/docs/shit_tsepochki_vvod_uzo_avtomat.xlsx
+++ b/docs/shit_tsepochki_vvod_uzo_avtomat.xlsx
@@ -11858,7 +11858,7 @@
     </row>
     <row r="61">
       <c r="A61" s="11" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B61" s="22" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
     </row>
     <row r="62">
       <c r="A62" s="11" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B62" s="22" t="inlineStr">
         <is>
@@ -12136,6 +12136,7 @@
         </is>
       </c>
     </row>
+    <row r="75"/>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
@@ -13775,7 +13776,7 @@
     </row>
     <row r="14">
       <c r="A14" s="17" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
@@ -13810,7 +13811,7 @@
     </row>
     <row r="15">
       <c r="A15" s="17" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
@@ -14462,7 +14463,7 @@
       </c>
       <c r="G32" s="23" t="inlineStr">
         <is>
-          <t>может = №60 или отдельно · Коммутатор вне щита AT62; в щите только клеммы UTP/PoE на R1.</t>
+          <t>может = №59 или отдельно · Коммутатор вне щита AT62; в щите только клеммы UTP/PoE на R1.</t>
         </is>
       </c>
     </row>
@@ -22155,7 +22156,7 @@
     </row>
     <row r="99">
       <c r="A99" s="63" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B99" s="63" t="inlineStr">
         <is>
@@ -22170,7 +22171,7 @@
     </row>
     <row r="100">
       <c r="A100" s="63" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B100" s="63" t="inlineStr">
         <is>
@@ -32039,7 +32040,7 @@
     </row>
     <row r="74">
       <c r="A74" s="32" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B74" s="32" t="inlineStr">
         <is>
@@ -32104,7 +32105,7 @@
     </row>
     <row r="75">
       <c r="A75" s="32" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B75" s="32" t="inlineStr">
         <is>
@@ -33284,7 +33285,7 @@
       </c>
       <c r="M92" s="32" t="inlineStr">
         <is>
-          <t>может = №60 или отдельно</t>
+          <t>может = №59 или отдельно</t>
         </is>
       </c>
     </row>
